--- a/Squark-Dashboard-Review-Actions-Sep-2026.xlsx
+++ b/Squark-Dashboard-Review-Actions-Sep-2026.xlsx
@@ -216,7 +216,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 of 34 are already done. 8 are partly there. 10 have not been started. 6 are waiting on a decision.</t>
+          <t xml:space="preserve">10 of 34 are already done. 9 are partly there. 9 have not been started. 6 are waiting on a decision.</t>
         </is>
       </c>
     </row>
@@ -484,12 +484,12 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">The board is open to everyone. capacity.view sits inside VIEW_BASICS (permissions-catalog.ts:126), which every role inherits, and the comment above it records why: "Matrix 2026-08-12: the capacity board is open to the whole organisation — knowing who is busy is not privileged." The routes are gated on capacity.view (capacity.module.ts:800,808), so moving the code moves the whole board.</t>
+          <t xml:space="preserve">The board is open to everyone. capacity.view sits inside VIEW_BASICS (permissions-catalog.ts:126), which every role inherits, and the comment above it records why: "Matrix 2026-08-12: the capacity board is open to the whole organisation — knowing who is free this week is not privileged." Worth knowing: the Senior Research Associate block still carries a stale comment saying "no capacity board" (:204), which the inheritance three lines later contradicts — so the intent has already drifted once.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Restricting it reverses a decision the permission matrix took deliberately in August, so it needs saying out loud rather than quietly changing. It is a small change — drop capacity.view out of VIEW_BASICS and add it to Senior Research Associate and above — but it also removes the project Capacity tab from everyone below that line, and a regrant on Contabo.</t>
+          <t xml:space="preserve">Restricting it reverses a decision the permission matrix took deliberately in August, so it needs saying out loud rather than quietly changing. Take capacity.view out of VIEW_BASICS and grant it from Senior Research Associate upwards, fix the stale comment, and regrant on Contabo. It also removes the project Capacity tab from everyone below that line.</t>
         </is>
       </c>
     </row>
@@ -529,19 +529,19 @@
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not started</t>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partly done</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Availability is only ever reached person-first. Nothing in the task screens consults capacity: neither the task detail panel nor the add-task flow looks at who is free, and the board’s own assignment starts from a person (you click their row, then pick the work). Staffing a task today means guessing, or opening the board in another tab.</t>
+          <t xml:space="preserve">One narrow case already works. The coverage-at-risk panel starts from a task and offers a "Reassign to…" list of free teammates with their free hours beside them (app/capacity/page.tsx:433-462, fed by capacity.module.ts:744-753), and BD deal staffing exposes the same free-hours figure. Everywhere else is person-first: the board is rows of people, and neither the task detail panel nor the add-task flow consults availability at all.</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Put availability where the task is: on the assignee picker, show each candidate’s free hours over the task’s date range, most free first. The capacity API already returns exactly that per person per day — this is a new view onto data that exists, not new arithmetic.</t>
+          <t xml:space="preserve">Generalise what the coverage panel already does to any task, not only a task caught behind someone’s leave. On the assignee picker, show each candidate’s free hours over the task’s own date range, most free first — the capacity API already returns exactly that per person per day.</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two of the four places already search. The People directory filters on name and email (app/users/page.tsx:85-86), and the task assignee picker has its own search box (TaskDetailPanel.tsx:139,250-251). The two that do not are both on projects: the Project Manager dropdown on the create form and the add-member dropdown on the Overview tab.</t>
+          <t xml:space="preserve">Two of the four places already search, and neither searches enough. The People directory filters on name and email only (app/users/page.tsx:84-87) — not designation, department, office or status, though it shows all four in the table. The task assignee picker has its own search over name and email (TaskDetailPanel.tsx:139,250-251). The two with no search at all are both on projects: the Project Manager dropdown on the create form and the add-member dropdown on the Overview tab. The capacity board’s own people search is name-only.</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Give the two project pickers the same search the task picker already has. At 28 people a plain dropdown still works, so this is about the next 28 rather than today.</t>
+          <t xml:space="preserve">Make one searchable person picker, matching name, email, designation and department, and use it in all four places. The patent picker on the project form is already this shape and is the thing to copy.</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not Super Admin only. Every org-wide route is gated on analytics.view.organization (performance.module.ts:49-73), which Manager holds outright (permissions-catalog.ts:154), and Admin and Super Admin inherit. Everyone else — Senior Consultant, Consultant, Senior Research Associate, Employee, HR, BD — holds analytics.view.own and sees their own figures only (:191,235,264,286).</t>
+          <t xml:space="preserve">Not Super Admin only, and there is a dead permission in the way. The org-wide routes are gated on analytics.view.organization (performance.module.ts:49-73), held by Manager (permissions-catalog.ts:154), Admin and Super Admin. Everyone else holds analytics.view.own and sees themselves. Separately, HR is granted performance.view.organization (:287) — a code that is never checked anywhere in the codebase, so it grants nothing; HR sees only its own figures.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">If it is to be Super Admin alone, take analytics.view.organization off Manager and off Admin, which the August matrix deliberately gave them. Decide first whether people keep their own figures (analytics.view.own) or lose those too. Needs a regrant on Contabo.</t>
+          <t xml:space="preserve">If it is to be Super Admin alone, take analytics.view.organization off Manager and off Admin, which the August matrix deliberately gave them, and decide whether people keep analytics.view.own for their own figures. Delete the dead performance.view.organization grant while you are there. Needs a regrant on Contabo.</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">A per-person overdue count exists: tasksOverdue counts tasks assigned to the person that are past their due date and not closed (performance.service.ts:141-146). But it counts by who holds the task NOW, not by who held it when it breached — so reassigning a late task moves the breach onto the person who inherited it, and a task closed late is not counted at all once it closes.</t>
+          <t xml:space="preserve">A per-person overdue count exists — tasksOverdue counts tasks assigned to the person that are past due and not closed (performance.service.ts:145), shown as "Open · Overdue" on the personal panel. But it counts by who holds the task NOW, not who held it when it breached, so reassigning a late task moves the breach onto whoever inherited it, and a task closed late stops being counted the moment it closes. The org leaderboard carries no overdue figure at all (performance.service.ts:438-444), and nothing in the codebase records a breach as an event.</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decide what "under who" means, then record it. Attributing a breach to the holder at the moment it breached needs the breach captured when it happens — the overdue sweep already runs daily and already knows, so it is the natural place to write it down.</t>
+          <t xml:space="preserve">Decide what "under who" means, then record it when it happens rather than recomputing it. The overdue sweep already runs daily and already knows which tasks have just gone past their date — that is the natural place to write down who was holding it.</t>
         </is>
       </c>
     </row>
@@ -2378,10 +2378,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="12">
         <v>1</v>
@@ -2578,10 +2578,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" s="12">
         <v>6</v>
